--- a/src/indices_info_completed.xlsx
+++ b/src/indices_info_completed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\charl\Desktop\eutops\MultiOmics_IntermittentFasting\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE52DF49-F2BB-4989-BFA3-0D2AE543842A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFD816A-82E0-4C8A-9E8C-1D9812C1ABFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="765" yWindow="2025" windowWidth="25755" windowHeight="17295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
